--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="841">
   <si>
-    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1788 merged PRs)</t>
+    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1794 merged PRs)</t>
   </si>
   <si>
     <t>DONE = verified on main (branch merged or files present) · NEEDS-VERIFY = weak signal, not trusted until GUARD confirms · PENDING = needs build · PENDING (GATED) = financial/locked, needs Jorge's gate first</t>
@@ -12636,7 +12636,7 @@
         <v>839</v>
       </c>
       <c r="B9">
-        <v>1788</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -12644,7 +12644,7 @@
         <v>840</v>
       </c>
       <c r="B10">
-        <v>7688</v>
+        <v>7694</v>
       </c>
     </row>
   </sheetData>

--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="841">
   <si>
-    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1794 merged PRs)</t>
+    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1809 merged PRs)</t>
   </si>
   <si>
     <t>DONE = verified on main (branch merged or files present) · NEEDS-VERIFY = weak signal, not trusted until GUARD confirms · PENDING = needs build · PENDING (GATED) = financial/locked, needs Jorge's gate first</t>
@@ -12636,7 +12636,7 @@
         <v>839</v>
       </c>
       <c r="B9">
-        <v>1794</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -12644,7 +12644,7 @@
         <v>840</v>
       </c>
       <c r="B10">
-        <v>7694</v>
+        <v>7703</v>
       </c>
     </row>
   </sheetData>

--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-03.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="841">
   <si>
-    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1809 merged PRs)</t>
+    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-07-03 (verified vs origin/main + 1835 merged PRs)</t>
   </si>
   <si>
     <t>DONE = verified on main (branch merged or files present) · NEEDS-VERIFY = weak signal, not trusted until GUARD confirms · PENDING = needs build · PENDING (GATED) = financial/locked, needs Jorge's gate first</t>
@@ -12636,7 +12636,7 @@
         <v>839</v>
       </c>
       <c r="B9">
-        <v>1809</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -12644,7 +12644,7 @@
         <v>840</v>
       </c>
       <c r="B10">
-        <v>7703</v>
+        <v>7709</v>
       </c>
     </row>
   </sheetData>
